--- a/docentes/Hernández López Elizabeth - Estadisticos 20241.xlsx
+++ b/docentes/Hernández López Elizabeth - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="27">
   <si>
     <t>Mat</t>
   </si>
@@ -82,31 +82,22 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>PALOMARES</t>
-  </si>
-  <si>
-    <t>ROSALES</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>RAYMUNDO</t>
-  </si>
-  <si>
-    <t>JUSTIN GIOVANNI</t>
-  </si>
-  <si>
-    <t>DORIAN</t>
+    <t>CALIHUA</t>
+  </si>
+  <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>CAMPOS</t>
+  </si>
+  <si>
+    <t>JOANNA JAQUELINE</t>
+  </si>
+  <si>
+    <t>ANGEL CHARBEL</t>
   </si>
 </sst>
 </file>
@@ -676,16 +667,19 @@
         <v>33</v>
       </c>
       <c r="D2">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>90.91</v>
+      </c>
+      <c r="H2">
+        <v>7.8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -699,16 +693,19 @@
         <v>21</v>
       </c>
       <c r="D3">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>85.70999999999999</v>
+      </c>
+      <c r="H3">
+        <v>6.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -722,16 +719,19 @@
         <v>25</v>
       </c>
       <c r="D4">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>84</v>
+      </c>
+      <c r="H4">
+        <v>6.7</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -745,16 +745,19 @@
         <v>19</v>
       </c>
       <c r="D5">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>84.20999999999999</v>
+      </c>
+      <c r="H5">
+        <v>7.1</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -768,16 +771,19 @@
         <v>21</v>
       </c>
       <c r="D6">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>95.23999999999999</v>
+      </c>
+      <c r="H6">
+        <v>7.4</v>
       </c>
     </row>
   </sheetData>
@@ -833,16 +839,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G2">
-        <v>84.84999999999999</v>
+        <v>90.91</v>
       </c>
       <c r="H2">
-        <v>7.8</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -859,16 +865,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="G3">
-        <v>61.9</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H3">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -885,16 +891,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G4">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="H4">
-        <v>6.7</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -911,16 +917,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G5">
-        <v>68.42</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="H5">
-        <v>7.1</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -937,16 +943,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G6">
-        <v>80.95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="H6">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -956,7 +962,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -988,22 +994,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920247</v>
+        <v>24330051920382</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1011,47 +1017,24 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920308</v>
+        <v>22330051920050</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>23330051920207</v>
-      </c>
-      <c r="B4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G4">
         <v>2</v>
       </c>
     </row>

--- a/docentes/Hernández López Elizabeth - Estadisticos 20241.xlsx
+++ b/docentes/Hernández López Elizabeth - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="36">
   <si>
     <t>Mat</t>
   </si>
@@ -85,16 +85,43 @@
     <t>CALIHUA</t>
   </si>
   <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
+    <t>PELAYO</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
     <t>ZEPAHUA</t>
   </si>
   <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
+    <t>MACUIXTLE</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>VALIENTE</t>
+  </si>
+  <si>
     <t>CAMPOS</t>
   </si>
   <si>
     <t>JOANNA JAQUELINE</t>
+  </si>
+  <si>
+    <t>MARIA FERNANDA</t>
+  </si>
+  <si>
+    <t>IVAN JESUS</t>
+  </si>
+  <si>
+    <t>DIEGO DE JESUS</t>
   </si>
   <si>
     <t>ANGEL CHARBEL</t>
@@ -962,7 +989,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1000,10 +1027,10 @@
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1017,25 +1044,94 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920050</v>
+        <v>23330051920220</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D3" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G3">
         <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>23330051920309</v>
+      </c>
+      <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>23330051920191</v>
+      </c>
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>22330051920050</v>
+      </c>
+      <c r="B6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Hernández López Elizabeth - Estadisticos 20241.xlsx
+++ b/docentes/Hernández López Elizabeth - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="41">
   <si>
     <t>Mat</t>
   </si>
@@ -82,6 +82,12 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
     <t>CALIHUA</t>
   </si>
   <si>
@@ -97,6 +103,9 @@
     <t>ZEPAHUA</t>
   </si>
   <si>
+    <t>CORTES</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
@@ -110,6 +119,12 @@
   </si>
   <si>
     <t>CAMPOS</t>
+  </si>
+  <si>
+    <t>CARLOS</t>
+  </si>
+  <si>
+    <t>FERNANDA YAMILET</t>
   </si>
   <si>
     <t>JOANNA JAQUELINE</t>
@@ -989,7 +1004,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1021,39 +1036,39 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920382</v>
+        <v>23330051920301</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920220</v>
+        <v>23330051920271</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D3" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -1062,27 +1077,27 @@
         <v>12</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920309</v>
+        <v>24330051920382</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D4" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1090,22 +1105,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920191</v>
+        <v>23330051920220</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D5" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1113,24 +1128,70 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920050</v>
+        <v>23330051920309</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D6" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
       </c>
       <c r="F6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>23330051920191</v>
+      </c>
+      <c r="B7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" t="s">
+        <v>39</v>
+      </c>
+      <c r="E7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>22330051920050</v>
+      </c>
+      <c r="B8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D8" t="s">
+        <v>40</v>
+      </c>
+      <c r="E8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" t="s">
         <v>11</v>
       </c>
-      <c r="G6">
+      <c r="G8">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Hernández López Elizabeth - Estadisticos 20241.xlsx
+++ b/docentes/Hernández López Elizabeth - Estadisticos 20241.xlsx
@@ -82,64 +82,64 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>CALIHUA</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
     <t>ORTIZ</t>
   </si>
   <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>CALIHUA</t>
-  </si>
-  <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
     <t>PELAYO</t>
   </si>
   <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>VALIENTE</t>
+  </si>
+  <si>
+    <t>CAMPOS</t>
+  </si>
+  <si>
+    <t>MACUIXTLE</t>
   </si>
   <si>
     <t>CORTES</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>MACUIXTLE</t>
-  </si>
-  <si>
     <t>TORRES</t>
   </si>
   <si>
-    <t>VALIENTE</t>
-  </si>
-  <si>
-    <t>CAMPOS</t>
+    <t>FERNANDA YAMILET</t>
+  </si>
+  <si>
+    <t>JOANNA JAQUELINE</t>
+  </si>
+  <si>
+    <t>DIEGO DE JESUS</t>
+  </si>
+  <si>
+    <t>ANGEL CHARBEL</t>
+  </si>
+  <si>
+    <t>MARIA FERNANDA</t>
   </si>
   <si>
     <t>CARLOS</t>
   </si>
   <si>
-    <t>FERNANDA YAMILET</t>
-  </si>
-  <si>
-    <t>JOANNA JAQUELINE</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
     <t>IVAN JESUS</t>
-  </si>
-  <si>
-    <t>DIEGO DE JESUS</t>
-  </si>
-  <si>
-    <t>ANGEL CHARBEL</t>
   </si>
 </sst>
 </file>
@@ -994,7 +994,7 @@
         <v>95.23999999999999</v>
       </c>
       <c r="H6">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1036,7 +1036,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920301</v>
+        <v>23330051920271</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
@@ -1051,38 +1051,38 @@
         <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920271</v>
+        <v>24330051920382</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D3" t="s">
         <v>35</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920382</v>
+        <v>23330051920191</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
@@ -1094,10 +1094,10 @@
         <v>36</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1105,7 +1105,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920220</v>
+        <v>22330051920050</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
@@ -1120,15 +1120,15 @@
         <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920309</v>
+        <v>23330051920220</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
@@ -1143,15 +1143,15 @@
         <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920191</v>
+        <v>23330051920301</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
@@ -1166,15 +1166,15 @@
         <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920050</v>
+        <v>23330051920309</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
@@ -1189,7 +1189,7 @@
         <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G8">
         <v>1</v>

--- a/docentes/Hernández López Elizabeth - Estadisticos 20241.xlsx
+++ b/docentes/Hernández López Elizabeth - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="27">
   <si>
     <t>Mat</t>
   </si>
@@ -82,64 +82,22 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>CALIHUA</t>
+    <t>FLORES</t>
   </si>
   <si>
     <t>GARCIA</t>
   </si>
   <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>PELAYO</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
+    <t>LAGUNA</t>
   </si>
   <si>
     <t>VALIENTE</t>
   </si>
   <si>
-    <t>CAMPOS</t>
-  </si>
-  <si>
-    <t>MACUIXTLE</t>
-  </si>
-  <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>FERNANDA YAMILET</t>
-  </si>
-  <si>
-    <t>JOANNA JAQUELINE</t>
+    <t>JOSE ANTONIO</t>
   </si>
   <si>
     <t>DIEGO DE JESUS</t>
-  </si>
-  <si>
-    <t>ANGEL CHARBEL</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>CARLOS</t>
-  </si>
-  <si>
-    <t>IVAN JESUS</t>
   </si>
 </sst>
 </file>
@@ -881,16 +839,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G2">
-        <v>90.91</v>
+        <v>96.97</v>
       </c>
       <c r="H2">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -907,16 +865,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G3">
-        <v>85.70999999999999</v>
+        <v>90.48</v>
       </c>
       <c r="H3">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -933,16 +891,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G4">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="H4">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -959,16 +917,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G5">
-        <v>84.20999999999999</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="H5">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1004,7 +962,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1036,22 +994,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920271</v>
+        <v>22330051920389</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D2" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G2">
         <v>3</v>
@@ -1059,139 +1017,24 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920382</v>
+        <v>23330051920191</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D3" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>23330051920191</v>
-      </c>
-      <c r="B4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D4" t="s">
-        <v>36</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>22330051920050</v>
-      </c>
-      <c r="B5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D5" t="s">
-        <v>37</v>
-      </c>
-      <c r="E5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>23330051920220</v>
-      </c>
-      <c r="B6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" t="s">
-        <v>31</v>
-      </c>
-      <c r="D6" t="s">
-        <v>38</v>
-      </c>
-      <c r="E6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>23330051920301</v>
-      </c>
-      <c r="B7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" t="s">
-        <v>32</v>
-      </c>
-      <c r="D7" t="s">
-        <v>39</v>
-      </c>
-      <c r="E7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" t="s">
-        <v>13</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>23330051920309</v>
-      </c>
-      <c r="B8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" t="s">
-        <v>33</v>
-      </c>
-      <c r="D8" t="s">
-        <v>40</v>
-      </c>
-      <c r="E8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" t="s">
-        <v>13</v>
-      </c>
-      <c r="G8">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Hernández López Elizabeth - Estadisticos 20241.xlsx
+++ b/docentes/Hernández López Elizabeth - Estadisticos 20241.xlsx
@@ -1012,7 +1012,7 @@
         <v>11</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:7">
